--- a/artfynd/A 52973-2022 artfynd.xlsx
+++ b/artfynd/A 52973-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121139218</v>
       </c>
       <c r="B2" t="n">
-        <v>105732</v>
+        <v>105742</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 52973-2022 artfynd.xlsx
+++ b/artfynd/A 52973-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121139218</v>
       </c>
       <c r="B2" t="n">
-        <v>105742</v>
+        <v>105755</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 52973-2022 artfynd.xlsx
+++ b/artfynd/A 52973-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121139218</v>
       </c>
       <c r="B2" t="n">
-        <v>105755</v>
+        <v>105756</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 52973-2022 artfynd.xlsx
+++ b/artfynd/A 52973-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121139218</v>
       </c>
       <c r="B2" t="n">
-        <v>105756</v>
+        <v>105759</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
